--- a/TruScore logic/OPEN Pillar.xlsx
+++ b/TruScore logic/OPEN Pillar.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TrueScan-FoodScanner\TruScore logic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22840C8B-1749-424D-B7CD-4FF50088DA68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B52F87F-EDFD-448A-B297-AB4BF3FFD08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BB904EBE-EC27-4577-B392-A9CA08F804A9}"/>
+    <workbookView xWindow="33735" yWindow="750" windowWidth="23055" windowHeight="14730" xr2:uid="{BB904EBE-EC27-4577-B392-A9CA08F804A9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="63">
   <si>
     <t xml:space="preserve">Pillar (25 pts) </t>
   </si>
@@ -111,9 +111,6 @@
     <t xml:space="preserve"> brands_tags (parent map present) </t>
   </si>
   <si>
-    <t xml:space="preserve"> Hidden/opaque parent=-5 </t>
-  </si>
-  <si>
     <t xml:space="preserve"> Overall Pillar Cap </t>
   </si>
   <si>
@@ -126,9 +123,6 @@
     <t xml:space="preserve"> 1. Applied after all adjustments; overrides if &lt;0. </t>
   </si>
   <si>
-    <t xml:space="preserve"> Uniform 15 consistency; OECD defends without negativity; fair to indies avoids X backlash on bias. Ditched geo-weight for MVP\\'97embed mandates in elements. </t>
-  </si>
-  <si>
     <t xml:space="preserve"> Ingredients Disclosure </t>
   </si>
   <si>
@@ -144,59 +138,89 @@
     <t xml:space="preserve"> ingredients_text (present) </t>
   </si>
   <si>
-    <t xml:space="preserve"> Present=+2, none=-5 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Modest deduct for no digital record (defensible if not public); accounts for possible packaging list not digitized. </t>
-  </si>
-  <si>
     <t xml:space="preserve"> 1. Country OFF &gt; 2. Global OFF &gt; 3. Local govt regs (e.g., MHLW Japan) &gt; 4. User subs if gaps; binary present/none. </t>
   </si>
   <si>
     <t xml:space="preserve"> FDA (US), Health Canada, FSANZ (AU/NZ), UK FSA/EFSA, MHLW (Japan), CFS (HK irritants), SFA (SG) &gt; Country/Global OFF </t>
   </si>
   <si>
-    <t xml:space="preserve"> 1=-5, 2=-10, &gt;=3=-15; if NOVA&gt;=3; zero hidden &amp; NOVA1-2 = +5; zero hidden &amp; NOVA3-4 = +2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Studies/X defend count; geo local tags heavy. Comprehensive hidden catalog conceals nasties\\'97focus opacity proxy. Mandate embed: +5/+2 rewards for zero hidden tied to NOVA. </t>
-  </si>
-  <si>
     <t xml:space="preserve"> 1. Country OFF &gt; 2. Global OFF &gt; 3. Local govt (e.g., SFA SG); deduct if match; conditional NOVA tie; reward if zero hidden. </t>
   </si>
   <si>
     <t xml:space="preserve"> FDA (US), Health Canada, FSANZ (AU/NZ origins), UK FSA/EFSA, MHLW (Japan), CFS (HK), SFA (SG) &gt; Country/Global OFF </t>
   </si>
   <si>
-    <t xml:space="preserve"> No origin=-8, complete=+7 bonus </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Studies defend; heavy geo for supply chain shocks; GS1 API post-MVP (costs &gt;$5k, post-2027 enhancement for AI-422 origin/AI-423 processing deduct -8 missing). Increased bonus to +7 incentivise good behaviour. </t>
-  </si>
-  <si>
     <t xml:space="preserve"> 1. Country OFF &gt; 2. Global OFF &gt; 3. Local govt tags (e.g., FSANZ AU); deduct if missing, bonus if complete; GS1 post-MVP. </t>
   </si>
   <si>
     <t xml:space="preserve"> Country/Global OFF </t>
   </si>
   <si>
-    <t xml:space="preserve"> 70% hate indie illusions (10 corps control 33k products\\'97X sentiment 2025) </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Sentiment defends; virality on "Owned By Nestle Alert" shares. Mandate embed here\\'97no base complexity. </t>
-  </si>
-  <si>
     <t xml:space="preserve"> 1. Country OFF &gt; 2. Global OFF; deduct if hidden parent; GS1 post-MVP for ownership. </t>
   </si>
   <si>
-    <t xml:space="preserve"> Caps final Open score at min 0; zero "opacity alert" callout on hidden crap\\'97viral rage without overkill. </t>
+    <t xml:space="preserve"> Uniform 15 consistency; OECD defends without negativity; fair to indies avoids X backlash on bias. Ditched geo-weight for MVP'97embed mandates in elements. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Present=+2, none=-3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Modest deduct for no digital record (defensible if not public); accounts for possible packaging list not digitized. Adjusted to -3 for fairness on sparse DB entries. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1=-4, 2=-8, &gt;=3=-11; if NOVA&gt;=3; zero hidden &amp; NOVA1-2 = +4; zero hidden &amp; NOVA3-4 = +2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Studies/X defend count; geo local tags heavy. Comprehensive hidden catalog conceals nasties'97focus opacity proxy. Mandate embed: +4/+2 rewards for zero hidden tied to NOVA. Softer deducts for balance per beta insights. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Nutritional Information </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Full nutritional information disclosed with benchmarks </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> FDA (US nutrition labels), Health Canada, FSANZ (AU/NZ), UK FSA/EFSA, MHLW (Japan), CFS (HK), SFA (SG) &gt; Country/Global OFF </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 55% distrust hidden nutrients/sugar (obesity concerns X 2025) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> nutrients (complete array with _100g keys and serving_size) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Complete (per 100g/serve benchmarks)=+3, partial=+1, none=-3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Rewards transparent benchmarks per WHO/EFSA studies; virality on sugar hides without overkill. Ties to G20 mandates (e.g., EU per-100g). </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. Country OFF &gt; 2. Global OFF; bonus if nutrients complete with _100g/serve; partial if only totals. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> No origin=-4, complete=+4 bonus </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Studies defend; heavy geo for supply chain shocks; GS1 API post-MVP (costs &gt;$5k, post-2027 enhancement for AI-422 origin/AI-423 processing deduct -4 missing). Softer bonus/deduct to balance per beta. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 70% hate indie illusions (10 corps control 33k products'97X sentiment 2025) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Hidden/opaque parent=-3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Sentiment defends; virality on "Owned By Nestle Alert" shares. Mandate embed here'97no base complexity. Softer deduct for fairness. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Caps final Open score at min 0; zero "opacity alert" callout on hidden crap'97viral rage without overkill. </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -217,19 +241,19 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE2D5"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -249,9 +273,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -261,8 +282,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -578,7 +602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21C149CC-AACB-4AE3-BE1E-B17C8CB58521}">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.85546875" customWidth="1"/>
@@ -596,212 +620,239 @@
     <row r="1" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="122.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="6" t="s">
+      <c r="A2" s="4"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="K2" s="4" t="s">
+      <c r="J2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="95.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="3" t="s">
+      <c r="A3" s="4"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="H3" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="I3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="142.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="3" t="s">
+      <c r="A4" s="4"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G4" s="4" t="s">
+      <c r="F4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>45</v>
+      <c r="I4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="95.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="K5" s="4" t="s">
+      <c r="A5" s="4"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="2" t="s">
         <v>49</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="96" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>53</v>
+      <c r="A6" s="4"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="6"/>
-      <c r="D7" s="3" t="s">
+      <c r="C7" s="4"/>
+      <c r="D7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="C8" s="4"/>
+      <c r="D8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="H8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="4" t="s">
+      <c r="I8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="4" t="s">
+      <c r="J8" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="K8" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>32</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:A6"/>
-    <mergeCell ref="C2:C7"/>
+    <mergeCell ref="C2:C8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
